--- a/data/results.xlsx
+++ b/data/results.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -608,6 +608,66 @@
         </is>
       </c>
     </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Deepak Yadav</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr"/>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Error: 'Model' object has no attribute 'supported_generation_methods'</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Error: 'Model' object has no attribute 'supported_generation_methods'</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Error: 'Model' object has no attribute 'supported_generation_methods'</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Error: 'Model' object has no attribute 'supported_generation_methods'</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Arjun Mehta</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Backend Developer</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Error: 404 NOT_FOUND. {'error': {'code': 404, 'message': 'models/gemini-1.5-flash is not found for API version v1beta, or is not supported for generateContent. Call ListModels to see the list of available models and their supported methods.', 'status': 'NOT_FOUND'}}</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Error: 404 NOT_FOUND. {'error': {'code': 404, 'message': 'models/gemini-1.5-flash is not found for API version v1beta, or is not supported for generateContent. Call ListModels to see the list of available models and their supported methods.', 'status': 'NOT_FOUND'}}</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Error: 404 NOT_FOUND. {'error': {'code': 404, 'message': 'models/gemini-1.5-flash is not found for API version v1beta, or is not supported for generateContent. Call ListModels to see the list of available models and their supported methods.', 'status': 'NOT_FOUND'}}</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Error: 404 NOT_FOUND. {'error': {'code': 404, 'message': 'models/gemini-1.5-flash is not found for API version v1beta, or is not supported for generateContent. Call ListModels to see the list of available models and their supported methods.', 'status': 'NOT_FOUND'}}</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
